--- a/data/availability/projects/lmd/zoya.xlsx
+++ b/data/availability/projects/lmd/zoya.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Q4 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Q4 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cabin</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1309,7 +1309,6 @@
       <c r="G2" t="n">
         <v>93</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoon Views</t>
@@ -1320,7 +1319,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Q4 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1366,7 +1365,6 @@
       <c r="G3" t="n">
         <v>123</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoon Views</t>
@@ -1377,7 +1375,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Q4 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1423,7 +1421,6 @@
       <c r="G4" t="n">
         <v>115</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoon Views</t>
@@ -1434,7 +1431,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1480,7 +1477,6 @@
       <c r="G5" t="n">
         <v>145</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoon Views</t>
@@ -1491,7 +1487,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1513,7 +1509,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cabin</t>
+          <t>Chalet</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1537,7 +1533,6 @@
       <c r="G6" t="n">
         <v>66</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoon Views</t>
@@ -1609,7 +1604,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1655,7 +1650,6 @@
       <c r="G8" t="n">
         <v>230</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoon Views</t>
@@ -1666,7 +1660,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1712,7 +1706,6 @@
       <c r="G9" t="n">
         <v>300</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoon Views</t>
@@ -1723,7 +1716,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1769,7 +1762,6 @@
       <c r="G10" t="n">
         <v>260</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoon Views</t>
@@ -1780,7 +1772,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1826,7 +1818,6 @@
       <c r="G11" t="n">
         <v>495</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoon Views</t>
@@ -1837,7 +1828,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
